--- a/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yara est dans sa chambre. Elle construit une cabane. Papa plie une couverture. Le nez de Yara chatouille. Atchoum. Yara sent le nez plein. Papa ouvre le tiroir. Il tend un mouchoir. Yara prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Parce qu'elle a pris un mouchoir, elle respire mieux. Papa montre la poubelle. Yara va jeter. Elle met le mouchoir dans la poubelle. Papa dit : mouchoir, puis poubelle. Plus tard, ils vont dans la cuisine. Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.</t>
+          <t>Yara est dans sa chambre. Elle construit une cabane. Papa plie une couverture. Le nez de Yara chatouille. Atchoum. Yara sent le nez plein. Papa ouvre le tiroir. Il tend un mouchoir. Yara prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Parce qu'elle a pris un mouchoir, elle respire mieux. Papa montre la poubelle. Yara va jeter. Elle met le mouchoir dans la poubelle. Mouchoir, puis poubelle. Plus tard, ils vont dans la cuisine. Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Yara est dans sa chambre. Elle construit une cabane. Papa plie une couverture. Le nez de Yara chatouille. Atchoum. Yara sent le nez plein. Papa ouvre le tiroir. Il tend un mouchoir. Yara prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Parce qu'elle a pris un mouchoir, elle respire mieux. Papa montre la poubelle. Yara va jeter. Elle met le mouchoir dans la poubelle.
+papa|Mouchoir, puis poubelle. Plus tard, ils vont dans la cuisine.
+narrateur|Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le nez de Yara chatouille. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Yara a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Yara pose un coussin dans la cabane. Papa s'assoit près d'elle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Le nez de Yara chatouille. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Yara a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1841,7 @@
           <t>narrateur|Yara pose un coussin dans la cabane. Papa s'assoit près d'elle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yara et le mouchoir</t>
+          <t>La cabane et le mouchoir de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deux chaises tiennent un drap. Un coussin dépasse. Le nez de Mila chatouille. Mouchoir, puis poubelle, dans la chambre puis la cuisine.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yara est dans sa chambre. Elle construit une cabane. Papa plie une couverture. Le nez de Yara chatouille. Atchoum. Yara sent le nez plein. Papa ouvre le tiroir. Il tend un mouchoir. Yara prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Parce qu'elle a pris un mouchoir, elle respire mieux. Papa montre la poubelle. Yara va jeter. Elle met le mouchoir dans la poubelle. Mouchoir, puis poubelle. Plus tard, ils vont dans la cuisine. Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.</t>
+          <t>Deux chaises tiennent un drap blanc. Le drap est un peu froissé. Un coussin rouge dépasse en dessous. Papa plie une autre couverture. La couverture sent le linge propre. Mila, ta cabane est presque prête. Le drap est tout blanc. Oui. Un peu froissé. Le coussin dépasse. On le pousse tout doux. En ce moment, Mila rampe sous le drap. L'ombre est douce, là-dessous. Le nez de Mila chatouille. Atchoum. Ton nez est plein ? Oui, papa. Papa ouvre le tiroir. Il tend un mouchoir. Prends un mouchoir. Mila prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Je respire mieux. Parce que tu as pris un mouchoir. Papa montre la poubelle. Mouchoir, puis poubelle. Mila va jeter. Elle met le mouchoir dans la poubelle. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Tu as fini de jeter ? Oui, papa. Plus tard, ils vont dans la cuisine. Un verre d'eau attend sur la table. La table est lisse et froide. Tu bois un peu ? Oui. L'eau est fraîche. Le nez chatouille encore. Atchoum. Encore un mouchoir. Mila prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Mouchoir, puis poubelle. Ici aussi. Oui. Bravo, Mila. Mila se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, papa. Elle revient près de papa. Son nez est calme. On rentre dans la cabane ? Oui. Le coussin t'attend. Le drap blanc fait une ombre ronde. Mila rampe encore dessous. C'est doux, ici. La couverture sent le propre. Mon nez est libre. Parce que tu as pris un mouchoir. Puis la poubelle. Deux fois, chambre et cuisine. Oui. Bravo. C'est du bon travail. Le coussin rouge est bien au milieu. Les deux chaises tiennent encore le drap.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Yara est dans sa chambre. Elle construit une cabane. Papa plie une couverture. Le nez de Yara chatouille. Atchoum. Yara sent le nez plein. Papa ouvre le tiroir. Il tend un mouchoir. Yara prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Parce qu'elle a pris un mouchoir, elle respire mieux. Papa montre la poubelle. Yara va jeter. Elle met le mouchoir dans la poubelle.
-papa|Mouchoir, puis poubelle. Plus tard, ils vont dans la cuisine.
-narrateur|Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.</t>
+          <t>narrateur|Deux chaises tiennent un drap blanc.
+narrateur|Le drap est un peu froissé.
+narrateur|Un coussin rouge dépasse en dessous.
+narrateur|Papa plie une autre couverture.
+narrateur|La couverture sent le linge propre.
+papa|Mila, ta cabane est presque prête.
+enfant-f|Le drap est tout blanc.
+papa|Oui. Un peu froissé.
+enfant-f|Le coussin dépasse.
+papa|On le pousse tout doux.
+narrateur|En ce moment, Mila rampe sous le drap.
+narrateur|L'ombre est douce, là-dessous.
+narrateur|Le nez de Mila chatouille.
+enfant-f|Atchoum.
+papa|Ton nez est plein ?
+enfant-f|Oui, papa.
+narrateur|Papa ouvre le tiroir.
+narrateur|Il tend un mouchoir.
+papa|Prends un mouchoir.
+narrateur|Mila prend un mouchoir.
+narrateur|Le papier est doux.
+narrateur|Elle se mouche.
+papa|Le nez est plus libre.
+enfant-f|Je respire mieux.
+papa|Parce que tu as pris un mouchoir.
+narrateur|Papa montre la poubelle.
+papa|Mouchoir, puis poubelle.
+narrateur|Mila va jeter.
+narrateur|Elle met le mouchoir dans la poubelle.
+papa|Bravo. Tu as jeté le mouchoir.
+papa|C'est du bon travail.
+papa|Tu as fini de jeter ?
+enfant-f|Oui, papa.
+narrateur|Plus tard, ils vont dans la cuisine.
+narrateur|Un verre d'eau attend sur la table.
+narrateur|La table est lisse et froide.
+papa|Tu bois un peu ?
+enfant-f|Oui. L'eau est fraîche.
+narrateur|Le nez chatouille encore.
+enfant-f|Atchoum.
+papa|Encore un mouchoir.
+narrateur|Mila prend un autre mouchoir.
+narrateur|Elle se mouche.
+narrateur|Elle jette dans la poubelle de la cuisine.
+papa|Mouchoir, puis poubelle.
+enfant-f|Ici aussi.
+papa|Oui. Bravo, Mila.
+narrateur|Mila se lave les mains.
+narrateur|L'eau est tiède.
+papa|Tu as fini de laver tes mains ?
+enfant-f|Oui, papa.
+narrateur|Elle revient près de papa.
+narrateur|Son nez est calme.
+enfant-f|On rentre dans la cabane ?
+papa|Oui. Le coussin t'attend.
+narrateur|Le drap blanc fait une ombre ronde.
+narrateur|Mila rampe encore dessous.
+enfant-f|C'est doux, ici.
+papa|La couverture sent le propre.
+enfant-f|Mon nez est libre.
+papa|Parce que tu as pris un mouchoir.
+papa|Puis la poubelle.
+enfant-f|Deux fois, chambre et cuisine.
+papa|Oui. Bravo. C'est du bon travail.
+narrateur|Le coussin rouge est bien au milieu.
+narrateur|Les deux chaises tiennent encore le drap.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>drap_cabane</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le nez de Yara chatouille. Que prend-elle ?</t>
+          <t>Le nez de Mila chatouille. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1577,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le nez de Yara chatouille. Que prend-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le nez de Mila chatouille.
+narrateur|Que prend-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yara a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
+          <t>Mila a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. Le drap blanc est encore un peu froissé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1749,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Yara a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a pris un mouchoir.
+narrateur|Elle s'est mouchée.
+narrateur|Elle a jeté le mouchoir à la poubelle.
+papa|Tu as pris un mouchoir ?
+enfant-f|Oui. Puis poubelle.
+papa|Bravo. C'est du bon travail.
+narrateur|Le drap blanc est encore un peu froissé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Yara pose un coussin dans la cabane. Papa s'assoit près d'elle.</t>
+          <t>Mila pose un coussin dans la cabane. Le coussin est rouge et moelleux. Je m'assois près de toi ? Oui. Sous le drap. Papa s'assoit près d'elle. L'ombre de la cabane est douce. Mon nez est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1918,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Yara pose un coussin dans la cabane. Papa s'assoit près d'elle.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila pose un coussin dans la cabane.
+narrateur|Le coussin est rouge et moelleux.
+papa|Je m'assois près de toi ?
+enfant-f|Oui. Sous le drap.
+narrateur|Papa s'assoit près d'elle.
+narrateur|L'ombre de la cabane est douce.
+enfant-f|Mon nez est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Mila. Le drap blanc tient encore sur les chaises. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,10 +2091,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Mouchoir, puis poubelle.
+papa|Bravo, Mila.
+narrateur|Le drap blanc tient encore sur les chaises.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Deux chaises tiennent un drap blanc. Le drap est un peu froissé. Un coussin rouge dépasse en dessous. Papa plie une autre couverture. La couverture sent le linge propre. Mila, ta cabane est presque prête. Le drap est tout blanc. Oui. Un peu froissé. Le coussin dépasse. On le pousse tout doux. En ce moment, Mila rampe sous le drap. L'ombre est douce, là-dessous. Le nez de Mila chatouille. Atchoum. Ton nez est plein ? Oui, papa. Papa ouvre le tiroir. Il tend un mouchoir. Prends un mouchoir. Mila prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Je respire mieux. Parce que tu as pris un mouchoir. Papa montre la poubelle. Mouchoir, puis poubelle. Mila va jeter. Elle met le mouchoir dans la poubelle. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Tu as fini de jeter ? Oui, papa. Plus tard, ils vont dans la cuisine. Un verre d'eau attend sur la table. La table est lisse et froide. Tu bois un peu ? Oui. L'eau est fraîche. Le nez chatouille encore. Atchoum. Encore un mouchoir. Mila prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Mouchoir, puis poubelle. Ici aussi. Oui. Bravo, Mila. Mila se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, papa. Elle revient près de papa. Son nez est calme. On rentre dans la cabane ? Oui. Le coussin t'attend. Le drap blanc fait une ombre ronde. Mila rampe encore dessous. C'est doux, ici. La couverture sent le propre. Mon nez est libre. Parce que tu as pris un mouchoir. Puis la poubelle. Deux fois, chambre et cuisine. Oui. Bravo. C'est du bon travail. Le coussin rouge est bien au milieu. Les deux chaises tiennent encore le drap.</t>
+          <t>Deux chaises tiennent un drap blanc. Le drap est un peu froissé. Un coussin rouge dépasse en dessous. Papa plie une autre couverture. La couverture sent le linge propre. Mila, ta cabane est presque prête. Le drap est tout blanc. Oui. Un peu froissé. Le coussin dépasse. On le pousse tout doux. En ce moment, Mila rampe sous le drap. L'ombre est douce, là-dessous. Le nez de Mila chatouille. Atchoum. Ton nez est plein ? Oui, papa. Papa ouvre le tiroir. Il tend un mouchoir. Prends un mouchoir. Mila prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Je respire mieux. Parce que tu as pris un mouchoir. Papa montre la poubelle. Mouchoir, puis poubelle. Mila va jeter. Elle met le mouchoir dans la poubelle. Bravo. Tu as jeté le mouchoir. Tu as fini de jeter ? Oui, papa. Plus tard, ils vont dans la cuisine. Un verre d'eau attend sur la table. La table est lisse et froide. Tu bois un peu ? Oui. L'eau est fraîche. Le nez chatouille encore. Atchoum. Encore un mouchoir. Mila prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Mouchoir, puis poubelle. Ici aussi. Oui. Bravo, Mila. Mila se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, papa. Elle revient près de papa. Son nez est calme. On rentre dans la cabane ? Oui. Le coussin t'attend. Le drap blanc fait une ombre ronde. Mila rampe encore dessous. C'est doux, ici. La couverture sent le propre. Mon nez est libre. Parce que tu as pris un mouchoir. Puis la poubelle. Deux fois, chambre et cuisine. Le coussin rouge est bien au milieu. Les deux chaises tiennent encore le drap.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yara est dans sa chambre. Elle construit une cabane. Papa plie une couverture. Le nez de Yara chatouille. Atchoum. Yara sent le nez plein. Papa ouvre le tiroir. Il tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Yara prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Parce qu'elle a pris un mouchoir, elle respire mieux. Papa montre la poubelle. Yara va jeter. Elle met le mouchoir dans la poubelle. Papa dit : mouchoir, puis poubelle. Plus tard, ils vont dans la cuisine. Yara boit de l'eau. Le nez chatouille encore. Yara prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Papa sourit. Yara se lave les mains. L'eau est tiède. Elle revient près de papa. Son nez est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Deux chaises tiennent un drap blanc. Le drap est un peu froissé. Un coussin rouge dépasse en dessous. Papa plie une autre couverture. La couverture sent le linge propre. Mila, ta cabane est presque prête. Le drap est tout blanc. Oui. Un peu froissé. Le coussin dépasse. On le pousse tout doux. En ce moment, Mila rampe sous le drap. L'ombre est douce, là-dessous. Le nez de Mila chatouille. Atchoum. Ton nez est plein ? Oui, papa. Papa ouvre le tiroir. Il tend un mouchoir. Prends un mouchoir. Mila prend un mouchoir. Le papier est doux. Elle se mouche. Le nez est plus libre. Je respire mieux. Parce que tu as pris un mouchoir. Papa montre la poubelle. Mouchoir, puis poubelle. Mila va jeter. Elle met le mouchoir dans la poubelle. Bravo. Tu as jeté le mouchoir. Tu as fini de jeter ? Oui, papa. Plus tard, ils vont dans la cuisine. Un verre d'eau attend sur la table. La table est lisse et froide. Tu bois un peu ? Oui. L'eau est fraîche. Le nez chatouille encore. Atchoum. Encore un mouchoir. Mila prend un autre mouchoir. Elle se mouche. Elle jette dans la poubelle de la cuisine. Mouchoir, puis poubelle. Ici aussi. Oui. Bravo, Mila. Mila se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, papa. Elle revient près de papa. Son nez est calme. On rentre dans la cabane ? Oui. Le coussin t'attend. Le drap blanc fait une ombre ronde. Mila rampe encore dessous. C'est doux, ici. La couverture sent le propre. Mon nez est libre. Parce que tu as pris un mouchoir. Puis la poubelle. Deux fois, chambre et cuisine. Le coussin rouge est bien au milieu. Les deux chaises tiennent encore le drap.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1354,7 +1354,6 @@
 narrateur|Mila va jeter.
 narrateur|Elle met le mouchoir dans la poubelle.
 papa|Bravo. Tu as jeté le mouchoir.
-papa|C'est du bon travail.
 papa|Tu as fini de jeter ?
 enfant-f|Oui, papa.
 narrateur|Plus tard, ils vont dans la cuisine.
@@ -1387,7 +1386,6 @@
 papa|Parce que tu as pris un mouchoir.
 papa|Puis la poubelle.
 enfant-f|Deux fois, chambre et cuisine.
-papa|Oui. Bravo. C'est du bon travail.
 narrateur|Le coussin rouge est bien au milieu.
 narrateur|Les deux chaises tiennent encore le drap.</t>
         </is>
@@ -1426,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le nez de Yara chatouille. Que prend-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le nez de Mila chatouille. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1605,12 +1603,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. Le drap blanc est encore un peu froissé.</t>
+          <t>Mila a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Le drap blanc est encore un peu froissé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yara a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Le drap blanc est encore un peu froissé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,7 +1752,6 @@
 narrateur|Elle a jeté le mouchoir à la poubelle.
 papa|Tu as pris un mouchoir ?
 enfant-f|Oui. Puis poubelle.
-papa|Bravo. C'est du bon travail.
 narrateur|Le drap blanc est encore un peu froissé.</t>
         </is>
       </c>
@@ -1787,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yara pose un coussin dans la cabane. Papa s'assoit près d'elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila pose un coussin dans la cabane. Le coussin est rouge et moelleux. Je m'assois près de toi ? Oui. Sous le drap. Papa s'assoit près d'elle. L'ombre de la cabane est douce. Mon nez est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1951,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mouchoir, puis poubelle. Bravo, Mila. Le drap blanc tient encore sur les chaises. L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Mila. Le drap blanc tient encore sur les chaises.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mouchoir, puis poubelle. Bravo, Mila. Le drap blanc tient encore sur les chaises.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,8 +2090,7 @@
         <is>
           <t>enfant-f|Mouchoir, puis poubelle.
 papa|Bravo, Mila.
-narrateur|Le drap blanc tient encore sur les chaises.
-narrateur|L'histoire est finie.</t>
+narrateur|Le drap blanc tient encore sur les chaises.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, cabane de draps, cuisine</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yara, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
